--- a/Task Report/Work item list/work list excell/New pending task.xlsx
+++ b/Task Report/Work item list/work list excell/New pending task.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shahid Raza\Capitall\VSA project functionality\Task Report\Work item list\work list excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4361AB5-11F8-44C8-8FDF-E94B874E63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0EE28D-9243-418E-8F53-78C624F7AB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{65BD65AB-347B-4BAB-9C5F-30C021D0C3BE}"/>
   </bookViews>
@@ -683,6 +683,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008034D6D5FD3F314393BD3DED1E7D912D" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac3e49493af0d70e377155e6b8349f5c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="affe18f8-2c16-492b-9b47-5374ed54faa0" xmlns:ns4="27a551d9-798f-4814-b65e-8370286c1742" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29c0e58eaa008cebc2391949e27aaa74" ns3:_="" ns4:_="">
     <xsd:import namespace="affe18f8-2c16-492b-9b47-5374ed54faa0"/>
@@ -871,15 +880,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -889,6 +889,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6207E42C-8419-4469-A8FA-ECD0B52B83C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E9E5FA-4792-4AB8-82B7-A4A8B7563D09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -907,14 +915,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6207E42C-8419-4469-A8FA-ECD0B52B83C8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA7E9626-5B53-42C7-9423-19A41154702D}">
   <ds:schemaRefs>
